--- a/pcb/bill_of_materials.xlsx
+++ b/pcb/bill_of_materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="131">
   <si>
     <t>No.</t>
   </si>
@@ -82,58 +82,52 @@
     <t>3</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>32Mhz</t>
-  </si>
-  <si>
-    <t>OSC-TH_BD3.0-P1.10-D0.4</t>
-  </si>
-  <si>
-    <t>DT-38 32.768KHz</t>
-  </si>
-  <si>
-    <t>KDS(大真空)</t>
-  </si>
-  <si>
-    <t>C93228</t>
+    <t>1117-3.3</t>
+  </si>
+  <si>
+    <t>AMS1117-5.0</t>
+  </si>
+  <si>
+    <t>SOT-223-3_L6.4-W3.5-P2.30-LS7.0-BR</t>
+  </si>
+  <si>
+    <t>IDCHIP(英锐芯)</t>
+  </si>
+  <si>
+    <t>C5125088</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>1117-3.3</t>
-  </si>
-  <si>
-    <t>AMS1117-5.0</t>
-  </si>
-  <si>
-    <t>SOT-223-3_L6.4-W3.5-P2.30-LS7.0-BR</t>
-  </si>
-  <si>
-    <t>IDCHIP(英锐芯)</t>
-  </si>
-  <si>
-    <t>C5125088</t>
+    <t>ATMEGA328P-AU</t>
+  </si>
+  <si>
+    <t>ATMEGA328P</t>
+  </si>
+  <si>
+    <t>TQFP-32_L7.0-W7.0-P0.80-LS9.0-BL</t>
+  </si>
+  <si>
+    <t>MICROCHIP</t>
+  </si>
+  <si>
+    <t>C14877</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>AT24C32M/TR</t>
-  </si>
-  <si>
-    <t>AT24C3M</t>
-  </si>
-  <si>
-    <t>SOP-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>HGSEMI(华冠)</t>
-  </si>
-  <si>
-    <t>C2688466</t>
+    <t>AU5790D,112</t>
+  </si>
+  <si>
+    <t>AU5790D</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
   </si>
   <si>
     <t>8</t>
@@ -142,370 +136,274 @@
     <t>6</t>
   </si>
   <si>
-    <t>ATMEGA328P-AU</t>
-  </si>
-  <si>
-    <t>ATMEGA328P</t>
-  </si>
-  <si>
-    <t>TQFP-32_L7.0-W7.0-P0.80-LS9.0-BL</t>
-  </si>
-  <si>
-    <t>MICROCHIP</t>
-  </si>
-  <si>
-    <t>C14877</t>
-  </si>
-  <si>
-    <t>32</t>
+    <t>0.1u</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C0805</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>AU5790D,112</t>
-  </si>
-  <si>
-    <t>AU5790D</t>
-  </si>
-  <si>
-    <t>SOIC-8</t>
-  </si>
-  <si>
-    <t>AAA-BAT-029-K01</t>
-  </si>
-  <si>
-    <t>BT1</t>
-  </si>
-  <si>
-    <t>BAT-TH_AAA-BAT-029-K01</t>
-  </si>
-  <si>
-    <t>LOTES(嘉澤端子)</t>
-  </si>
-  <si>
-    <t>C962133</t>
+    <t>22p</t>
+  </si>
+  <si>
+    <t>C4,C5,C20,C21</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>C6,C25,C26</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C1,C2</t>
-  </si>
-  <si>
-    <t>C0805</t>
+    <t>220p</t>
+  </si>
+  <si>
+    <t>C22,C23</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>0.1u</t>
-  </si>
-  <si>
-    <t>C3</t>
+    <t>4.7u</t>
+  </si>
+  <si>
+    <t>C24</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>22p</t>
-  </si>
-  <si>
-    <t>C4,C5,C20,C21</t>
-  </si>
-  <si>
-    <t>C0603</t>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>CAP-SMD_L3.2-W1.6-R-RD</t>
+  </si>
+  <si>
+    <t>T494A105K016AT</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
+    <t>C122312</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>C6,C25,C26</t>
+    <t>SS12</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>SMA-L_L4.4-W2.6-LS5.0-RD</t>
+  </si>
+  <si>
+    <t>C379819</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>220p</t>
-  </si>
-  <si>
-    <t>C22,C23</t>
+    <t>AFA07-S09FCC-00</t>
+  </si>
+  <si>
+    <t>FPC1</t>
+  </si>
+  <si>
+    <t>FPC-SMD_AFA07-S09FCC-00</t>
+  </si>
+  <si>
+    <t>JS(钜硕电子)</t>
+  </si>
+  <si>
+    <t>C262343</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>4.7u</t>
-  </si>
-  <si>
-    <t>C24</t>
+    <t>B-2100S15P-A110</t>
+  </si>
+  <si>
+    <t>H1,H2</t>
+  </si>
+  <si>
+    <t>HDR-TH_15P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>Ckmtw(灿科盟)</t>
+  </si>
+  <si>
+    <t>C124373</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>CAP-SMD_L3.2-W1.6-R-RD</t>
-  </si>
-  <si>
-    <t>T494A105K016AT</t>
-  </si>
-  <si>
-    <t>KEMET</t>
-  </si>
-  <si>
-    <t>C122312</t>
+    <t>IL-AG5-10P-S3L2</t>
+  </si>
+  <si>
+    <t>INPUT,SUBDISPLAY1</t>
+  </si>
+  <si>
+    <t>CONN-TH_10P-P2.50_IL-AG5-10P-S3L2</t>
+  </si>
+  <si>
+    <t>JAE(日本航空电子)</t>
+  </si>
+  <si>
+    <t>C2891425</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>SS12</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>SMA-L_L4.4-W2.6-LS5.0-RD</t>
-  </si>
-  <si>
-    <t>C379819</t>
+    <t>470nH</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L1210</t>
+  </si>
+  <si>
+    <t>NLV32T-R47J-EFD</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>C295221</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>DS1307ZN+</t>
-  </si>
-  <si>
-    <t>DS1307Z</t>
-  </si>
-  <si>
-    <t>SOIC-8_L4.9-W4.0-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>ADI(亚德诺)/MAXIM(美信)</t>
-  </si>
-  <si>
-    <t>C3304433</t>
+    <t>CD4066BM</t>
+  </si>
+  <si>
+    <t>MC14066</t>
+  </si>
+  <si>
+    <t>SOIC-14_L8.7-W3.9-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>C353979</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>AFA07-S09FCC-00</t>
-  </si>
-  <si>
-    <t>FPC1</t>
-  </si>
-  <si>
-    <t>FPC-SMD_AFA07-S09FCC-00</t>
-  </si>
-  <si>
-    <t>JS(钜硕电子)</t>
-  </si>
-  <si>
-    <t>C262343</t>
+    <t>XL2515</t>
+  </si>
+  <si>
+    <t>MCP2515</t>
+  </si>
+  <si>
+    <t>SOP-18_L11.4-W7.6-P1.27-LS10.6-BL</t>
+  </si>
+  <si>
+    <t>XINLUDA(信路达)</t>
+  </si>
+  <si>
+    <t>C609744</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>B-2100S15P-A110</t>
-  </si>
-  <si>
-    <t>H1,H2</t>
-  </si>
-  <si>
-    <t>HDR-TH_15P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>Ckmtw(灿科盟)</t>
-  </si>
-  <si>
-    <t>C124373</t>
+    <t>9.1k</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>R0805</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>IL-AG5-10P-S3L2</t>
-  </si>
-  <si>
-    <t>INPUT,SUBDISPLAY</t>
-  </si>
-  <si>
-    <t>CONN-TH_10P-P2.50_IL-AG5-10P-S3L2</t>
-  </si>
-  <si>
-    <t>JAE(日本航空电子)</t>
-  </si>
-  <si>
-    <t>C2891425</t>
+    <t>2.4k</t>
+  </si>
+  <si>
+    <t>R21</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>470nH</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>L1210</t>
-  </si>
-  <si>
-    <t>NLV32T-R47J-EFD</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>C295221</t>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>R23</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>CD4066BM</t>
-  </si>
-  <si>
-    <t>MC14066</t>
-  </si>
-  <si>
-    <t>SOIC-14_L8.7-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>C353979</t>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R24,R25</t>
+  </si>
+  <si>
+    <t>RMC08051K1%N</t>
+  </si>
+  <si>
+    <t>Tyohm(幸亚电阻)</t>
+  </si>
+  <si>
+    <t>C269744</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>XL2515</t>
-  </si>
-  <si>
-    <t>MCP2515</t>
-  </si>
-  <si>
-    <t>SOP-18_L11.4-W7.6-P1.27-LS10.6-BL</t>
-  </si>
-  <si>
-    <t>XINLUDA(信路达)</t>
-  </si>
-  <si>
-    <t>C609744</t>
+    <t>2kΩ</t>
+  </si>
+  <si>
+    <t>R26,R27</t>
+  </si>
+  <si>
+    <t>RMC08052K1%N</t>
+  </si>
+  <si>
+    <t>C269745</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>3.3kΩ</t>
-  </si>
-  <si>
-    <t>R2,R3,R8</t>
-  </si>
-  <si>
-    <t>R0805</t>
-  </si>
-  <si>
-    <t>ERA6VEB4702V</t>
-  </si>
-  <si>
-    <t>PANASONIC(松下)</t>
-  </si>
-  <si>
-    <t>C490805</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>1.5MΩ</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>510kΩ</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>9.1k</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2.4k</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>10k</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R24,R25</t>
-  </si>
-  <si>
-    <t>RMC08051K1%N</t>
-  </si>
-  <si>
-    <t>Tyohm(幸亚电阻)</t>
-  </si>
-  <si>
-    <t>C269744</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>2kΩ</t>
-  </si>
-  <si>
-    <t>R26,R27</t>
-  </si>
-  <si>
-    <t>RMC08052K1%N</t>
-  </si>
-  <si>
-    <t>C269745</t>
+    <t>330Ω</t>
+  </si>
+  <si>
+    <t>R28,R29</t>
+  </si>
+  <si>
+    <t>R1206</t>
+  </si>
+  <si>
+    <t>RMC12063305%N</t>
+  </si>
+  <si>
+    <t>C269759</t>
   </si>
 </sst>
 </file>
@@ -882,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="20" customWidth="1"/>
@@ -1013,54 +911,54 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1083,71 +981,71 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
         <v>39</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
       <c r="F7" t="s">
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1165,39 +1063,39 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>20</v>
@@ -1205,19 +1103,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -1240,19 +1138,19 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -1275,34 +1173,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
@@ -1310,34 +1208,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K13" t="s">
         <v>20</v>
@@ -1345,136 +1243,136 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" t="s">
         <v>71</v>
       </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="I14" t="s">
         <v>72</v>
       </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
         <v>74</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>75</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>76</v>
       </c>
-      <c r="E15" t="s">
-        <v>68</v>
-      </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
         <v>80</v>
       </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>81</v>
-      </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s">
         <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
@@ -1485,174 +1383,174 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
         <v>107</v>
       </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>110</v>
-      </c>
       <c r="F21" t="s">
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K22" t="s">
         <v>20</v>
@@ -1660,101 +1558,101 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J23" t="s">
         <v>19</v>
       </c>
       <c r="K23" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H24" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="I24" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
       </c>
       <c r="K24" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H25" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="J25" t="s">
         <v>19</v>
@@ -1763,253 +1661,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
-        <v>136</v>
-      </c>
-      <c r="H26" t="s">
-        <v>137</v>
-      </c>
-      <c r="I26" t="s">
-        <v>138</v>
-      </c>
-      <c r="J26" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" t="s">
-        <v>135</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H27" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" t="s">
-        <v>138</v>
-      </c>
-      <c r="J27" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>145</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>146</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>148</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>154</v>
-      </c>
-      <c r="B31">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
-        <v>155</v>
-      </c>
-      <c r="D31" t="s">
-        <v>156</v>
-      </c>
-      <c r="E31" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" t="s">
-        <v>155</v>
-      </c>
-      <c r="G31" t="s">
-        <v>157</v>
-      </c>
-      <c r="H31" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31" t="s">
-        <v>159</v>
-      </c>
-      <c r="J31" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>160</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" t="s">
-        <v>162</v>
-      </c>
-      <c r="E32" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" t="s">
-        <v>161</v>
-      </c>
-      <c r="G32" t="s">
-        <v>163</v>
-      </c>
-      <c r="H32" t="s">
-        <v>158</v>
-      </c>
-      <c r="I32" t="s">
-        <v>164</v>
-      </c>
-      <c r="J32" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
         <v>15</v>
       </c>
     </row>

--- a/pcb/bill_of_materials.xlsx
+++ b/pcb/bill_of_materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="142">
   <si>
     <t>No.</t>
   </si>
@@ -202,6 +202,24 @@
     <t>12</t>
   </si>
   <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C28,C29,C30,C31</t>
+  </si>
+  <si>
+    <t>MBK0805X7R104K500NT</t>
+  </si>
+  <si>
+    <t>FH-BK(风华邦科)</t>
+  </si>
+  <si>
+    <t>C2830721</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>SS12</t>
   </si>
   <si>
@@ -214,7 +232,7 @@
     <t>C379819</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>AFA07-S09FCC-00</t>
@@ -232,7 +250,7 @@
     <t>C262343</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>B-2100S15P-A110</t>
@@ -250,7 +268,7 @@
     <t>C124373</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>IL-AG5-10P-S3L2</t>
@@ -268,7 +286,7 @@
     <t>C2891425</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>470nH</t>
@@ -289,7 +307,7 @@
     <t>C295221</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>CD4066BM</t>
@@ -307,7 +325,7 @@
     <t>C353979</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>XL2515</t>
@@ -325,7 +343,7 @@
     <t>C609744</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>9.1k</t>
@@ -337,7 +355,7 @@
     <t>R0805</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>2.4k</t>
@@ -346,7 +364,7 @@
     <t>R21</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>10k</t>
@@ -355,7 +373,7 @@
     <t>R23</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>1kΩ</t>
@@ -373,7 +391,7 @@
     <t>C269744</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>2kΩ</t>
@@ -388,22 +406,37 @@
     <t>C269745</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>330Ω</t>
-  </si>
-  <si>
-    <t>R28,R29</t>
+    <t>25</t>
+  </si>
+  <si>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R28,R29,R30</t>
   </si>
   <si>
     <t>R1206</t>
   </si>
   <si>
-    <t>RMC12063305%N</t>
-  </si>
-  <si>
-    <t>C269759</t>
+    <t>RMC12062205%N</t>
+  </si>
+  <si>
+    <t>C269757</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>100Ω</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>RMC12061005%N</t>
+  </si>
+  <si>
+    <t>C269751</t>
   </si>
 </sst>
 </file>
@@ -780,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="20" customWidth="1"/>
@@ -1211,7 +1244,7 @@
         <v>62</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -1220,19 +1253,19 @@
         <v>64</v>
       </c>
       <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" t="s">
         <v>65</v>
       </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -1243,28 +1276,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
         <v>69</v>
       </c>
-      <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>68</v>
-      </c>
       <c r="H14" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
         <v>72</v>
@@ -1273,7 +1306,7 @@
         <v>19</v>
       </c>
       <c r="K14" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1281,7 +1314,7 @@
         <v>73</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>74</v>
@@ -1308,7 +1341,7 @@
         <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1343,7 +1376,7 @@
         <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1351,7 +1384,7 @@
         <v>85</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
         <v>86</v>
@@ -1366,42 +1399,42 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" t="s">
         <v>89</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>90</v>
-      </c>
-      <c r="I17" t="s">
-        <v>91</v>
       </c>
       <c r="J17" t="s">
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" t="s">
         <v>93</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>94</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
         <v>95</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>93</v>
       </c>
       <c r="H18" t="s">
         <v>96</v>
@@ -1413,7 +1446,7 @@
         <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1448,7 +1481,7 @@
         <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1471,36 +1504,36 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
         <v>15</v>
@@ -1523,19 +1556,19 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" t="s">
         <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>107</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
@@ -1558,34 +1591,34 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
         <v>20</v>
@@ -1605,7 +1638,7 @@
         <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
         <v>121</v>
@@ -1614,10 +1647,10 @@
         <v>123</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J24" t="s">
         <v>19</v>
@@ -1628,28 +1661,28 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" t="s">
         <v>127</v>
-      </c>
-      <c r="E25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" t="s">
-        <v>126</v>
       </c>
       <c r="G25" t="s">
         <v>129</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
         <v>130</v>
@@ -1661,8 +1694,78 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" t="s">
+        <v>136</v>
+      </c>
+      <c r="J26" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" t="s">
+        <v>140</v>
+      </c>
+      <c r="H27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" t="s">
+        <v>141</v>
+      </c>
+      <c r="J27" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>15</v>
       </c>
     </row>

--- a/pcb/bill_of_materials.xlsx
+++ b/pcb/bill_of_materials.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="150">
   <si>
     <t>No.</t>
   </si>
@@ -205,7 +205,7 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>C28,C29,C30,C31</t>
+    <t>C28,C29,C30,C31,C32</t>
   </si>
   <si>
     <t>MBK0805X7R104K500NT</t>
@@ -220,6 +220,42 @@
     <t>13</t>
   </si>
   <si>
+    <t>330nF</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>CAP-SMD_L3.2-W1.6</t>
+  </si>
+  <si>
+    <t>CA45A-A-35V-0.33UF-K</t>
+  </si>
+  <si>
+    <t>CEC(振华新云)</t>
+  </si>
+  <si>
+    <t>C2976917</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>CAP-SMD_L3.2-W1.6-RD</t>
+  </si>
+  <si>
+    <t>CA45-A-35V-0.1UF-K</t>
+  </si>
+  <si>
+    <t>C2976900</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>SS12</t>
   </si>
   <si>
@@ -232,7 +268,7 @@
     <t>C379819</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>AFA07-S09FCC-00</t>
@@ -250,7 +286,7 @@
     <t>C262343</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>B-2100S15P-A110</t>
@@ -268,7 +304,7 @@
     <t>C124373</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
   </si>
   <si>
     <t>IL-AG5-10P-S3L2</t>
@@ -286,7 +322,7 @@
     <t>C2891425</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>470nH</t>
@@ -307,7 +343,7 @@
     <t>C295221</t>
   </si>
   <si>
-    <t>18</t>
+    <t>20</t>
   </si>
   <si>
     <t>CD4066BM</t>
@@ -325,7 +361,7 @@
     <t>C353979</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
   </si>
   <si>
     <t>XL2515</t>
@@ -343,7 +379,7 @@
     <t>C609744</t>
   </si>
   <si>
-    <t>20</t>
+    <t>22</t>
   </si>
   <si>
     <t>9.1k</t>
@@ -355,7 +391,7 @@
     <t>R0805</t>
   </si>
   <si>
-    <t>21</t>
+    <t>23</t>
   </si>
   <si>
     <t>2.4k</t>
@@ -364,7 +400,7 @@
     <t>R21</t>
   </si>
   <si>
-    <t>22</t>
+    <t>24</t>
   </si>
   <si>
     <t>10k</t>
@@ -373,54 +409,24 @@
     <t>R23</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R24,R25</t>
-  </si>
-  <si>
-    <t>RMC08051K1%N</t>
+    <t>25</t>
+  </si>
+  <si>
+    <t>220Ω</t>
+  </si>
+  <si>
+    <t>R28,R29,R30,R32</t>
+  </si>
+  <si>
+    <t>R1206</t>
+  </si>
+  <si>
+    <t>RMC12062205%N</t>
   </si>
   <si>
     <t>Tyohm(幸亚电阻)</t>
   </si>
   <si>
-    <t>C269744</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2kΩ</t>
-  </si>
-  <si>
-    <t>R26,R27</t>
-  </si>
-  <si>
-    <t>RMC08052K1%N</t>
-  </si>
-  <si>
-    <t>C269745</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>220Ω</t>
-  </si>
-  <si>
-    <t>R28,R29,R30</t>
-  </si>
-  <si>
-    <t>R1206</t>
-  </si>
-  <si>
-    <t>RMC12062205%N</t>
-  </si>
-  <si>
     <t>C269757</t>
   </si>
   <si>
@@ -437,6 +443,24 @@
   </si>
   <si>
     <t>C269751</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>78L09</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>SOT-89-3_L4.5-W2.5-P1.50-LS4.2-BR</t>
+  </si>
+  <si>
+    <t>DOWO(东沃)</t>
+  </si>
+  <si>
+    <t>C6718416</t>
   </si>
 </sst>
 </file>
@@ -813,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="20" customWidth="1"/>
@@ -1244,7 +1268,7 @@
         <v>62</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
@@ -1291,16 +1315,16 @@
         <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -1311,63 +1335,63 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s">
         <v>73</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" t="s">
-        <v>77</v>
-      </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J15" t="s">
         <v>19</v>
       </c>
       <c r="K15" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
         <v>81</v>
       </c>
-      <c r="E16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>80</v>
-      </c>
       <c r="H16" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="I16" t="s">
         <v>84</v>
@@ -1376,7 +1400,7 @@
         <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1384,7 +1408,7 @@
         <v>85</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
         <v>86</v>
@@ -1411,7 +1435,7 @@
         <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1419,7 +1443,7 @@
         <v>91</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
         <v>92</v>
@@ -1434,77 +1458,77 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" t="s">
         <v>95</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>96</v>
-      </c>
-      <c r="I18" t="s">
-        <v>97</v>
       </c>
       <c r="J18" t="s">
         <v>19</v>
       </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
         <v>98</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>99</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>100</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" t="s">
         <v>101</v>
       </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>102</v>
-      </c>
-      <c r="I19" t="s">
-        <v>103</v>
       </c>
       <c r="J19" t="s">
         <v>19</v>
       </c>
       <c r="K19" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>104</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>105</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>106</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
         <v>107</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>105</v>
       </c>
       <c r="H20" t="s">
         <v>108</v>
@@ -1516,7 +1540,7 @@
         <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1539,71 +1563,71 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="H21" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -1626,34 +1650,34 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K24" t="s">
         <v>20</v>
@@ -1661,34 +1685,34 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>130</v>
+        <v>15</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K25" t="s">
         <v>20</v>
@@ -1696,31 +1720,31 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" t="s">
         <v>133</v>
       </c>
-      <c r="E26" t="s">
-        <v>134</v>
-      </c>
-      <c r="F26" t="s">
-        <v>132</v>
-      </c>
       <c r="G26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J26" t="s">
         <v>19</v>
@@ -1731,31 +1755,31 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H27" t="s">
         <v>137</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" t="s">
-        <v>138</v>
-      </c>
-      <c r="G27" t="s">
-        <v>140</v>
-      </c>
-      <c r="H27" t="s">
-        <v>124</v>
-      </c>
       <c r="I27" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J27" t="s">
         <v>19</v>
@@ -1764,8 +1788,43 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H28" t="s">
+        <v>148</v>
+      </c>
+      <c r="I28" t="s">
+        <v>149</v>
+      </c>
+      <c r="J28" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>15</v>
       </c>
     </row>
